--- a/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,16 +466,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Telecaller</v>
+        <v>FOS</v>
       </c>
       <c r="B2" t="str">
-        <v>Josefa</v>
+        <v>rajivkubhartiajdeorugyhgkndflskrugherijgknverihfknlsrkgjkhikgnlerogufkjblvrbkegjfugthjlfuoghlgjerhgiefbjn</v>
       </c>
       <c r="C2" t="str">
-        <v>Wisoky</v>
+        <v>Stamm</v>
       </c>
       <c r="D2" t="str">
-        <v>14343</v>
+        <v>1005</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -484,28 +484,28 @@
         <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>23577359447</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>Agency Frontend</v>
+        <v>Agency Collection Staff Backend</v>
       </c>
       <c r="K2" t="str">
-        <v>Agent</v>
+        <v>Agency Owner</v>
       </c>
       <c r="L2" t="str">
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>8187749697</v>
+        <v>4640649503</v>
       </c>
       <c r="N2" t="str">
-        <v>josefa@yopmail.com</v>
+        <v>amely@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>re35sr</v>
+        <v>resr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FOS</v>
+        <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>rajivkubhartiajdeorugyhgkndflskrugherijgknverihfknlsrkgjkhikgnlerogufkjblvrbkegjfugthjlfuoghlgjerhgiefbjn</v>
+        <v>Melyssa</v>
       </c>
       <c r="C2" t="str">
-        <v>Stamm</v>
+        <v>Kerluke</v>
       </c>
       <c r="D2" t="str">
         <v>1005</v>
@@ -484,13 +484,13 @@
         <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>23577359447</v>
       </c>
       <c r="J2" t="str">
         <v>Agency Collection Staff Backend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>4640649503</v>
+        <v>4658742633</v>
       </c>
       <c r="N2" t="str">
-        <v>amely@yopmail.com</v>
+        <v>melyssa@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>resr</v>
+        <v>re35sr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,31 +466,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FOS</v>
+        <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Wade</v>
+        <v>Camille</v>
       </c>
       <c r="C2" t="str">
-        <v>Schamberger</v>
+        <v>Smitham</v>
       </c>
       <c r="D2" t="str">
-        <v>1270</v>
+        <v>1002</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>435ab#@#%4</v>
+        <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>23577359447</v>
       </c>
       <c r="J2" t="str">
         <v>Agency Collection Staff Backend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>4806832292</v>
+        <v>7909467984</v>
       </c>
       <c r="N2" t="str">
-        <v>wade@yopmail.com</v>
+        <v>camille@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>resr</v>
+        <v>re35sr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Telecaller</v>
+        <v>FOS</v>
       </c>
       <c r="B2" t="str">
-        <v>Camille</v>
+        <v>Mario</v>
       </c>
       <c r="C2" t="str">
-        <v>Smitham</v>
+        <v>Jerde-Pollich</v>
       </c>
       <c r="D2" t="str">
         <v>1002</v>
@@ -484,13 +484,13 @@
         <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>23577359447</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>Agency Collection Staff Backend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>7909467984</v>
+        <v>2431058670</v>
       </c>
       <c r="N2" t="str">
-        <v>camille@yopmail.com</v>
+        <v>mario@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>re35sr</v>
+        <v>resr</v>
       </c>
     </row>
   </sheetData>
